--- a/AAII_Financials/Yearly/OTSKY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/OTSKY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="92">
   <si>
     <t>OTSKY</t>
   </si>
@@ -894,16 +894,16 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>179100</v>
+        <v>-107100</v>
       </c>
       <c r="E14" s="3">
-        <v>801700</v>
+        <v>814700</v>
       </c>
       <c r="F14" s="3">
-        <v>1223200</v>
+        <v>1246300</v>
       </c>
       <c r="G14" s="3">
-        <v>314900</v>
+        <v>189600</v>
       </c>
       <c r="H14" s="3">
         <v>19000</v>
@@ -933,7 +933,7 @@
         <v>686800</v>
       </c>
       <c r="F15" s="3">
-        <v>664700</v>
+        <v>693600</v>
       </c>
       <c r="G15" s="3">
         <v>711000</v>
@@ -972,16 +972,16 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>12725000</v>
+        <v>13068000</v>
       </c>
       <c r="E17" s="3">
-        <v>12173200</v>
+        <v>12179500</v>
       </c>
       <c r="F17" s="3">
-        <v>12250800</v>
+        <v>12254000</v>
       </c>
       <c r="G17" s="3">
-        <v>11768400</v>
+        <v>11900000</v>
       </c>
       <c r="H17" s="3">
         <v>11739800</v>
@@ -1005,16 +1005,16 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>3021700</v>
+        <v>2678700</v>
       </c>
       <c r="E18" s="3">
-        <v>2645900</v>
+        <v>2639600</v>
       </c>
       <c r="F18" s="3">
-        <v>2069100</v>
+        <v>2065900</v>
       </c>
       <c r="G18" s="3">
-        <v>1410900</v>
+        <v>1279300</v>
       </c>
       <c r="H18" s="3">
         <v>1273100</v>
@@ -1053,16 +1053,16 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-214900</v>
+        <v>-163800</v>
       </c>
       <c r="E20" s="3">
-        <v>-213800</v>
+        <v>-287700</v>
       </c>
       <c r="F20" s="3">
-        <v>-144400</v>
+        <v>-165800</v>
       </c>
       <c r="G20" s="3">
-        <v>-43800</v>
+        <v>-217200</v>
       </c>
       <c r="H20" s="3">
         <v>-165800</v>
@@ -1086,16 +1086,16 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>3977500</v>
+        <v>3583400</v>
       </c>
       <c r="E21" s="3">
-        <v>3546500</v>
+        <v>3614200</v>
       </c>
       <c r="F21" s="3">
-        <v>2878300</v>
+        <v>2925400</v>
       </c>
       <c r="G21" s="3">
-        <v>2165800</v>
+        <v>2207500</v>
       </c>
       <c r="H21" s="3">
         <v>2175900</v>
@@ -1119,16 +1119,16 @@
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>172400</v>
+        <v>27000</v>
       </c>
       <c r="E22" s="3">
-        <v>55900</v>
+        <v>39300</v>
       </c>
       <c r="F22" s="3">
-        <v>46300</v>
+        <v>22900</v>
       </c>
       <c r="G22" s="3">
-        <v>46000</v>
+        <v>25200</v>
       </c>
       <c r="H22" s="3">
         <v>22700</v>
@@ -1194,7 +1194,7 @@
         <v>121700</v>
       </c>
       <c r="G24" s="3">
-        <v>270500</v>
+        <v>269500</v>
       </c>
       <c r="H24" s="3">
         <v>299000</v>
@@ -1260,7 +1260,7 @@
         <v>890300</v>
       </c>
       <c r="G26" s="3">
-        <v>1041000</v>
+        <v>1042100</v>
       </c>
       <c r="H26" s="3">
         <v>1122200</v>
@@ -1293,7 +1293,7 @@
         <v>862800</v>
       </c>
       <c r="G27" s="3">
-        <v>1015400</v>
+        <v>1016300</v>
       </c>
       <c r="H27" s="3">
         <v>1089700</v>
@@ -1449,16 +1449,16 @@
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>214900</v>
+        <v>163800</v>
       </c>
       <c r="E32" s="3">
-        <v>213800</v>
+        <v>287700</v>
       </c>
       <c r="F32" s="3">
-        <v>144400</v>
+        <v>165800</v>
       </c>
       <c r="G32" s="3">
-        <v>43800</v>
+        <v>217200</v>
       </c>
       <c r="H32" s="3">
         <v>165800</v>
@@ -1491,7 +1491,7 @@
         <v>862800</v>
       </c>
       <c r="G33" s="3">
-        <v>1015400</v>
+        <v>1016300</v>
       </c>
       <c r="H33" s="3">
         <v>1089700</v>
@@ -1557,7 +1557,7 @@
         <v>862800</v>
       </c>
       <c r="G35" s="3">
-        <v>1015400</v>
+        <v>1016300</v>
       </c>
       <c r="H35" s="3">
         <v>1089700</v>
@@ -1847,16 +1847,16 @@
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>2289900</v>
+        <v>3888200</v>
       </c>
       <c r="E47" s="3">
-        <v>2002200</v>
+        <v>3462100</v>
       </c>
       <c r="F47" s="3">
-        <v>1976100</v>
+        <v>3492000</v>
       </c>
       <c r="G47" s="3">
-        <v>1833200</v>
+        <v>3270700</v>
       </c>
       <c r="H47" s="3">
         <v>3770300</v>
@@ -2012,16 +2012,16 @@
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>1598200</v>
+        <v>0</v>
       </c>
       <c r="E52" s="3">
-        <v>1460000</v>
+        <v>0</v>
       </c>
       <c r="F52" s="3">
-        <v>1515900</v>
+        <v>0</v>
       </c>
       <c r="G52" s="3">
-        <v>1437600</v>
+        <v>0</v>
       </c>
       <c r="H52" s="3">
         <v>0</v>
@@ -2087,7 +2087,7 @@
         <v>23845000</v>
       </c>
       <c r="G54" s="3">
-        <v>23527500</v>
+        <v>23528100</v>
       </c>
       <c r="H54" s="3">
         <v>24500300</v>
@@ -2279,7 +2279,7 @@
         <v>1023300</v>
       </c>
       <c r="F61" s="3">
-        <v>893300</v>
+        <v>893200</v>
       </c>
       <c r="G61" s="3">
         <v>1137500</v>
@@ -2306,16 +2306,16 @@
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>698900</v>
+        <v>864900</v>
       </c>
       <c r="E62" s="3">
-        <v>577600</v>
+        <v>802500</v>
       </c>
       <c r="F62" s="3">
-        <v>306300</v>
+        <v>624700</v>
       </c>
       <c r="G62" s="3">
-        <v>415700</v>
+        <v>800400</v>
       </c>
       <c r="H62" s="3">
         <v>901100</v>
@@ -2447,7 +2447,7 @@
         <v>6561500</v>
       </c>
       <c r="G66" s="3">
-        <v>6371800</v>
+        <v>6371000</v>
       </c>
       <c r="H66" s="3">
         <v>6737400</v>
@@ -2627,7 +2627,7 @@
         <v>11501100</v>
       </c>
       <c r="G72" s="3">
-        <v>11777000</v>
+        <v>11778100</v>
       </c>
       <c r="H72" s="3">
         <v>12873200</v>
@@ -2759,7 +2759,7 @@
         <v>16981100</v>
       </c>
       <c r="G76" s="3">
-        <v>16874200</v>
+        <v>16875400</v>
       </c>
       <c r="H76" s="3">
         <v>17465900</v>
@@ -2863,7 +2863,7 @@
         <v>862800</v>
       </c>
       <c r="G81" s="3">
-        <v>1015400</v>
+        <v>1016300</v>
       </c>
       <c r="H81" s="3">
         <v>1089700</v>
@@ -2901,17 +2901,17 @@
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>72</v>
+      <c r="D83" s="3">
+        <v>740900</v>
+      </c>
+      <c r="E83" s="3">
+        <v>686800</v>
+      </c>
+      <c r="F83" s="3">
+        <v>693600</v>
+      </c>
+      <c r="G83" s="3">
+        <v>711000</v>
       </c>
       <c r="H83" s="3">
         <v>737000</v>
@@ -3099,17 +3099,17 @@
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>72</v>
+      <c r="D89" s="3">
+        <v>2574000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>2255700</v>
+      </c>
+      <c r="F89" s="3">
+        <v>2009300</v>
+      </c>
+      <c r="G89" s="3">
+        <v>1606500</v>
       </c>
       <c r="H89" s="3">
         <v>1987700</v>
@@ -3147,17 +3147,17 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>72</v>
+      <c r="D91" s="3">
+        <v>-560300</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-607800</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-643700</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-462200</v>
       </c>
       <c r="H91" s="3">
         <v>-455600</v>
@@ -3246,17 +3246,17 @@
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>72</v>
+      <c r="D94" s="3">
+        <v>-1030600</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-1690600</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-1351700</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-618600</v>
       </c>
       <c r="H94" s="3">
         <v>-827600</v>
@@ -3295,16 +3295,16 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>452700</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>424600</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>394800</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>421300</v>
       </c>
       <c r="H96" s="3">
         <v>486200</v>
@@ -3426,17 +3426,17 @@
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>72</v>
+      <c r="D100" s="3">
+        <v>-876000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-1204500</v>
+      </c>
+      <c r="F100" s="3">
+        <v>-427500</v>
+      </c>
+      <c r="G100" s="3">
+        <v>-724000</v>
       </c>
       <c r="H100" s="3">
         <v>-832400</v>
@@ -3459,17 +3459,17 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>72</v>
+      <c r="D101" s="3">
+        <v>24400</v>
+      </c>
+      <c r="E101" s="3">
+        <v>84900</v>
+      </c>
+      <c r="F101" s="3">
+        <v>65800</v>
+      </c>
+      <c r="G101" s="3">
+        <v>198300</v>
       </c>
       <c r="H101" s="3">
         <v>139800</v>
@@ -3493,16 +3493,16 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>691800</v>
       </c>
       <c r="E102" s="3">
-        <v>0</v>
+        <v>-554400</v>
       </c>
       <c r="F102" s="3">
-        <v>0</v>
+        <v>295900</v>
       </c>
       <c r="G102" s="3">
-        <v>0</v>
+        <v>462200</v>
       </c>
       <c r="H102" s="3">
         <v>467600</v>
